--- a/hrm/.plans/gop-db/warranty-repair-request/testcase.xlsx
+++ b/hrm/.plans/gop-db/warranty-repair-request/testcase.xlsx
@@ -567,7 +567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q125"/>
+  <dimension ref="A1:Q127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26.9" customWidth="1" min="1" max="1"/>
@@ -846,7 +846,7 @@
     <row r="11" ht="24" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Testcase _ Yêu cầu kiểm tra sửa chữa – bảo hành - Cập nhật ngày 20/08/2026</t>
+          <t>Testcase _ Yêu cầu kiểm tra sửa chữa – bảo hành - Cập nhật ngày 03/09/2026</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
@@ -6607,7 +6607,7 @@
       <c r="P102" s="16" t="inlineStr"/>
       <c r="Q102" s="16" t="inlineStr"/>
     </row>
-    <row r="103" ht="94" customHeight="1">
+    <row r="103" ht="115" customHeight="1">
       <c r="A103" s="15" t="inlineStr">
         <is>
           <t>YC sửa chữa - bảo hành</t>
@@ -6651,8 +6651,8 @@
       </c>
       <c r="I103" s="15" t="inlineStr">
         <is>
-          <t>- Mở tab mới hiển thị mẫu phiếu
-- Thấy khung tờ giấy dọc có viền, giấy nền trắng
+          <t>- Mở cửa sổ “Xem trước phiếu yêu cầu” ngay trên màn hình, không mở tab mới
+- Thấy đầy đủ tiêu đề công ty (logo, địa chỉ, điện thoại) ở đầu bản in
 - Trên phiếu có số phiếu, tên khách hàng, đủ 2 dòng thiết bị và khối ký tên (Người yêu cầu, Trưởng phòng yêu cầu, Phòng nhận yêu cầu, Ban giám đốc)
 - ⚠️ Không còn chỗ nào bỏ trống dạng ký hiệu chờ điền</t>
         </is>
@@ -6678,7 +6678,7 @@
       <c r="P103" s="16" t="inlineStr"/>
       <c r="Q103" s="16" t="inlineStr"/>
     </row>
-    <row r="104" ht="54" customHeight="1">
+    <row r="104" ht="72" customHeight="1">
       <c r="A104" s="15" t="inlineStr">
         <is>
           <t>YC sửa chữa - bảo hành</t>
@@ -6721,9 +6721,9 @@
       </c>
       <c r="I104" s="15" t="inlineStr">
         <is>
-          <t>- Không có thanh menu xanh phía trên, không hở dải màu lạ ở đầu trang
-- Nút In nằm bên phải, thẳng mép phải tờ giấy
-- 4 ô ký tên nằm ngang hàng, chia đều bề ngang</t>
+          <t>- Cửa sổ xem trước có tiêu đề “Xem trước phiếu yêu cầu” và nút In màu xanh ở góc trái trên
+- 4 ô ký tên nằm ngang hàng, chia đều bề ngang
+- Bấm dấu × hoặc phím Esc thì đóng cửa sổ, danh sách phía sau giữ nguyên bộ lọc</t>
         </is>
       </c>
       <c r="J104" s="15" t="inlineStr"/>
@@ -6747,7 +6747,7 @@
       <c r="P104" s="16" t="inlineStr"/>
       <c r="Q104" s="16" t="inlineStr"/>
     </row>
-    <row r="105" ht="67" customHeight="1">
+    <row r="105" ht="94" customHeight="1">
       <c r="A105" s="15" t="inlineStr">
         <is>
           <t>YC sửa chữa - bảo hành</t>
@@ -6791,10 +6791,10 @@
       </c>
       <c r="I105" s="15" t="inlineStr">
         <is>
-          <t>- Mở tab mới với mẫu danh sách khổ ngang, có khung tờ giấy
-- Tiêu đề “DANH SÁCH PHIẾU YÊU CẦU KIỂM TRA SỬA CHỮA BẢO HÀNH”
-- Bảng có đúng 4 phiếu đang lọc
-- Nền quanh tờ giấy cùng màu với trang in 1 phiếu</t>
+          <t>- Mở cửa sổ “Xem trước danh sách yêu cầu kiểm tra sửa chữa – bảo hành”
+- Tiêu đề bản in “DANH SÁCH PHIẾU YÊU CẦU KIỂM TRA SỬA CHỮA BẢO HÀNH”
+- Có 2 dòng “Thời gian” và “Phòng yêu cầu”; không lọc thì ghi “Tất cả”
+- Bảng có đúng 4 phiếu đang lọc, mỗi phiếu MỘT dòng dù có nhiều thiết bị</t>
         </is>
       </c>
       <c r="J105" s="15" t="inlineStr"/>
@@ -7023,7 +7023,7 @@
       <c r="P108" s="16" t="inlineStr"/>
       <c r="Q108" s="16" t="inlineStr"/>
     </row>
-    <row r="109" ht="34" customHeight="1">
+    <row r="109" ht="83" customHeight="1">
       <c r="A109" s="15" t="inlineStr">
         <is>
           <t>YC sửa chữa - bảo hành</t>
@@ -7041,23 +7041,23 @@
       </c>
       <c r="D109" s="15" t="inlineStr">
         <is>
-          <t>In danh sách khi chưa lọc gì</t>
+          <t>In danh sách khi chưa lọc gì — vượt trần in</t>
         </is>
       </c>
       <c r="E109" s="16" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="F109" s="15" t="inlineStr">
         <is>
-          <t>Không áp dụng bộ lọc nào, tổng 5.368 phiếu.</t>
+          <t>Không áp dụng bộ lọc nào, tổng hơn 5.000 phiếu.</t>
         </is>
       </c>
       <c r="G109" s="15" t="inlineStr">
         <is>
           <t>1. Bấm In danh sách
-2. Chờ trang xem trước tải xong</t>
+2. Đọc nội dung cửa sổ xem trước</t>
         </is>
       </c>
       <c r="H109" s="15" t="inlineStr">
@@ -7067,8 +7067,9 @@
       </c>
       <c r="I109" s="15" t="inlineStr">
         <is>
-          <t>- Trang hiện đủ số dòng tương ứng, không báo lỗi
-- ⚠️ Bản in rất dài, nên lọc trước khi in</t>
+          <t>- ⚠️ KHÔNG dựng bản in; cửa sổ chỉ hiện lời nhắc nền vàng: danh sách vượt mức in tối đa 2.000 dòng, đề nghị thu hẹp bộ lọc hoặc dùng Xuất Excel
+- Câu nhắc có ghi rõ số dòng thực tế của bộ lọc hiện tại
+- Trình duyệt KHÔNG bị treo, không mở hộp thoại in</t>
         </is>
       </c>
       <c r="J109" s="15" t="inlineStr"/>
@@ -7092,30 +7093,75 @@
       <c r="P109" s="16" t="inlineStr"/>
       <c r="Q109" s="16" t="inlineStr"/>
     </row>
-    <row r="110" ht="26" customHeight="1">
-      <c r="A110" s="13" t="n"/>
-      <c r="B110" s="13" t="n"/>
-      <c r="C110" s="14" t="inlineStr">
-        <is>
-          <t>VIII. RÀNG BUỘC NHẬP LIỆU</t>
-        </is>
-      </c>
-      <c r="D110" s="4" t="n"/>
-      <c r="E110" s="4" t="n"/>
-      <c r="F110" s="4" t="n"/>
-      <c r="G110" s="4" t="n"/>
-      <c r="H110" s="4" t="n"/>
-      <c r="I110" s="4" t="n"/>
-      <c r="J110" s="4" t="n"/>
-      <c r="K110" s="4" t="n"/>
-      <c r="L110" s="4" t="n"/>
-      <c r="M110" s="4" t="n"/>
-      <c r="N110" s="4" t="n"/>
-      <c r="O110" s="4" t="n"/>
-      <c r="P110" s="4" t="n"/>
-      <c r="Q110" s="5" t="n"/>
-    </row>
-    <row r="111" ht="75" customHeight="1">
+    <row r="110" ht="34" customHeight="1">
+      <c r="A110" s="15" t="inlineStr">
+        <is>
+          <t>YC sửa chữa - bảo hành</t>
+        </is>
+      </c>
+      <c r="B110" s="15" t="inlineStr">
+        <is>
+          <t>XUẤT EXCEL / IN</t>
+        </is>
+      </c>
+      <c r="C110" s="16" t="inlineStr">
+        <is>
+          <t>TC_07.011</t>
+        </is>
+      </c>
+      <c r="D110" s="15" t="inlineStr">
+        <is>
+          <t>In danh sách ngay dưới trần in</t>
+        </is>
+      </c>
+      <c r="E110" s="16" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F110" s="15" t="inlineStr">
+        <is>
+          <t>Lọc còn khoảng 1.900 phiếu (dưới 2.000).</t>
+        </is>
+      </c>
+      <c r="G110" s="15" t="inlineStr">
+        <is>
+          <t>1. Bấm In danh sách
+2. Chờ cửa sổ xem trước tải xong</t>
+        </is>
+      </c>
+      <c r="H110" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I110" s="15" t="inlineStr">
+        <is>
+          <t>- Bản in dựng bình thường, đủ số dòng, không hiện lời nhắc vượt trần</t>
+        </is>
+      </c>
+      <c r="J110" s="15" t="inlineStr"/>
+      <c r="K110" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="L110" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="M110" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="N110" s="15" t="inlineStr"/>
+      <c r="O110" s="16" t="inlineStr"/>
+      <c r="P110" s="16" t="inlineStr"/>
+      <c r="Q110" s="16" t="inlineStr"/>
+    </row>
+    <row r="111" ht="55" customHeight="1">
       <c r="A111" s="15" t="inlineStr">
         <is>
           <t>YC sửa chữa - bảo hành</t>
@@ -7123,34 +7169,33 @@
       </c>
       <c r="B111" s="15" t="inlineStr">
         <is>
-          <t>RÀNG BUỘC NHẬP LIỆU</t>
+          <t>XUẤT EXCEL / IN</t>
         </is>
       </c>
       <c r="C111" s="16" t="inlineStr">
         <is>
-          <t>TC_08.001</t>
+          <t>TC_07.012</t>
         </is>
       </c>
       <c r="D111" s="15" t="inlineStr">
         <is>
-          <t>Gửi đi khi bỏ trống các ô bắt buộc</t>
+          <t>Dòng tiến độ khi xuất Excel danh sách lớn</t>
         </is>
       </c>
       <c r="E111" s="16" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F111" s="15" t="inlineStr">
         <is>
-          <t>Phiếu nháp mới chỉ chọn khách hàng và 1 thiết bị, chưa nhập gì thêm.</t>
+          <t>Bộ lọc ra hơn 4.000 phiếu.</t>
         </is>
       </c>
       <c r="G111" s="15" t="inlineStr">
         <is>
-          <t>1. Bấm Lưu và gửi
-2. Bấm Xác nhận ở cửa sổ hỏi lại
-3. Quan sát các ô trên màn</t>
+          <t>1. Bấm Xuất Excel rồi Xuất file
+2. Quan sát dòng chữ cạnh nút trong lúc chờ</t>
         </is>
       </c>
       <c r="H111" s="15" t="inlineStr">
@@ -7160,9 +7205,9 @@
       </c>
       <c r="I111" s="15" t="inlineStr">
         <is>
-          <t>- Phiếu KHÔNG được gửi đi, vẫn ở màn đang sửa
-- Báo lỗi đỏ ngay dưới từng ô: Người liên hệ, Địa chỉ sửa chữa, Ghi chú, Phòng tiếp nhận xử lý và ô Mô tả yêu cầu của dòng thiết bị
-- Các ô lỗi có viền đỏ, dữ liệu đã nhập vẫn còn</t>
+          <t>- Hiện dòng “Đã tải …/… dòng”, sau đó “Đang dựng file …/… dòng”
+- Nút Xuất Excel bị khoá trong lúc chạy, xong thì mở lại
+- Tệp tải về đủ số dòng, không thiếu trang nào</t>
         </is>
       </c>
       <c r="J111" s="15" t="inlineStr"/>
@@ -7186,106 +7231,200 @@
       <c r="P111" s="16" t="inlineStr"/>
       <c r="Q111" s="16" t="inlineStr"/>
     </row>
-    <row r="112" ht="43" customHeight="1">
-      <c r="A112" s="15" t="inlineStr">
-        <is>
-          <t>YC sửa chữa - bảo hành</t>
-        </is>
-      </c>
-      <c r="B112" s="15" t="inlineStr">
+    <row r="112" ht="26" customHeight="1">
+      <c r="A112" s="13" t="n"/>
+      <c r="B112" s="13" t="n"/>
+      <c r="C112" s="14" t="inlineStr">
+        <is>
+          <t>VIII. RÀNG BUỘC NHẬP LIỆU</t>
+        </is>
+      </c>
+      <c r="D112" s="4" t="n"/>
+      <c r="E112" s="4" t="n"/>
+      <c r="F112" s="4" t="n"/>
+      <c r="G112" s="4" t="n"/>
+      <c r="H112" s="4" t="n"/>
+      <c r="I112" s="4" t="n"/>
+      <c r="J112" s="4" t="n"/>
+      <c r="K112" s="4" t="n"/>
+      <c r="L112" s="4" t="n"/>
+      <c r="M112" s="4" t="n"/>
+      <c r="N112" s="4" t="n"/>
+      <c r="O112" s="4" t="n"/>
+      <c r="P112" s="4" t="n"/>
+      <c r="Q112" s="5" t="n"/>
+    </row>
+    <row r="113" ht="75" customHeight="1">
+      <c r="A113" s="15" t="inlineStr">
+        <is>
+          <t>YC sửa chữa - bảo hành</t>
+        </is>
+      </c>
+      <c r="B113" s="15" t="inlineStr">
         <is>
           <t>RÀNG BUỘC NHẬP LIỆU</t>
         </is>
       </c>
-      <c r="C112" s="16" t="inlineStr">
+      <c r="C113" s="16" t="inlineStr">
+        <is>
+          <t>TC_08.001</t>
+        </is>
+      </c>
+      <c r="D113" s="15" t="inlineStr">
+        <is>
+          <t>Gửi đi khi bỏ trống các ô bắt buộc</t>
+        </is>
+      </c>
+      <c r="E113" s="16" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F113" s="15" t="inlineStr">
+        <is>
+          <t>Phiếu nháp mới chỉ chọn khách hàng và 1 thiết bị, chưa nhập gì thêm.</t>
+        </is>
+      </c>
+      <c r="G113" s="15" t="inlineStr">
+        <is>
+          <t>1. Bấm Lưu và gửi
+2. Bấm Xác nhận ở cửa sổ hỏi lại
+3. Quan sát các ô trên màn</t>
+        </is>
+      </c>
+      <c r="H113" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I113" s="15" t="inlineStr">
+        <is>
+          <t>- Phiếu KHÔNG được gửi đi, vẫn ở màn đang sửa
+- Báo lỗi đỏ ngay dưới từng ô: Người liên hệ, Địa chỉ sửa chữa, Ghi chú, Phòng tiếp nhận xử lý và ô Mô tả yêu cầu của dòng thiết bị
+- Các ô lỗi có viền đỏ, dữ liệu đã nhập vẫn còn</t>
+        </is>
+      </c>
+      <c r="J113" s="15" t="inlineStr"/>
+      <c r="K113" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="L113" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="M113" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="N113" s="15" t="inlineStr"/>
+      <c r="O113" s="16" t="inlineStr"/>
+      <c r="P113" s="16" t="inlineStr"/>
+      <c r="Q113" s="16" t="inlineStr"/>
+    </row>
+    <row r="114" ht="43" customHeight="1">
+      <c r="A114" s="15" t="inlineStr">
+        <is>
+          <t>YC sửa chữa - bảo hành</t>
+        </is>
+      </c>
+      <c r="B114" s="15" t="inlineStr">
+        <is>
+          <t>RÀNG BUỘC NHẬP LIỆU</t>
+        </is>
+      </c>
+      <c r="C114" s="16" t="inlineStr">
         <is>
           <t>TC_08.002</t>
         </is>
       </c>
-      <c r="D112" s="15" t="inlineStr">
+      <c r="D114" s="15" t="inlineStr">
         <is>
           <t>Gửi đi khi chưa chọn thiết bị nào</t>
         </is>
       </c>
-      <c r="E112" s="16" t="inlineStr">
+      <c r="E114" s="16" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="F112" s="15" t="inlineStr">
+      <c r="F114" s="15" t="inlineStr">
         <is>
           <t>Phiếu đã điền đủ thông tin chung nhưng bảng thiết bị đang trống.</t>
         </is>
       </c>
-      <c r="G112" s="15" t="inlineStr">
+      <c r="G114" s="15" t="inlineStr">
         <is>
           <t>1. Bấm Lưu và gửi rồi Xác nhận</t>
         </is>
       </c>
-      <c r="H112" s="15" t="inlineStr">
+      <c r="H114" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I112" s="15" t="inlineStr">
+      <c r="I114" s="15" t="inlineStr">
         <is>
           <t>- Hệ thống chặn, báo phải có ít nhất 1 thiết bị
 - ⚠️ Dòng chữ “Chưa chọn thiết bị nào…” trong bảng phải màu xám, không phải màu đỏ</t>
         </is>
       </c>
-      <c r="J112" s="15" t="inlineStr"/>
-      <c r="K112" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="L112" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="M112" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="N112" s="15" t="inlineStr"/>
-      <c r="O112" s="16" t="inlineStr"/>
-      <c r="P112" s="16" t="inlineStr"/>
-      <c r="Q112" s="16" t="inlineStr"/>
-    </row>
-    <row r="113" ht="47" customHeight="1">
-      <c r="A113" s="15" t="inlineStr">
-        <is>
-          <t>YC sửa chữa - bảo hành</t>
-        </is>
-      </c>
-      <c r="B113" s="15" t="inlineStr">
+      <c r="J114" s="15" t="inlineStr"/>
+      <c r="K114" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="L114" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="M114" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="N114" s="15" t="inlineStr"/>
+      <c r="O114" s="16" t="inlineStr"/>
+      <c r="P114" s="16" t="inlineStr"/>
+      <c r="Q114" s="16" t="inlineStr"/>
+    </row>
+    <row r="115" ht="47" customHeight="1">
+      <c r="A115" s="15" t="inlineStr">
+        <is>
+          <t>YC sửa chữa - bảo hành</t>
+        </is>
+      </c>
+      <c r="B115" s="15" t="inlineStr">
         <is>
           <t>RÀNG BUỘC NHẬP LIỆU</t>
         </is>
       </c>
-      <c r="C113" s="16" t="inlineStr">
+      <c r="C115" s="16" t="inlineStr">
         <is>
           <t>TC_08.003</t>
         </is>
       </c>
-      <c r="D113" s="15" t="inlineStr">
+      <c r="D115" s="15" t="inlineStr">
         <is>
           <t>Chặn chọn trùng serial trong cùng một phiếu</t>
         </is>
       </c>
-      <c r="E113" s="16" t="inlineStr">
+      <c r="E115" s="16" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="F113" s="15" t="inlineStr">
+      <c r="F115" s="15" t="inlineStr">
         <is>
           <t>Khách hàng có thiết bị đã khai serial trong hệ thống.</t>
         </is>
       </c>
-      <c r="G113" s="15" t="inlineStr">
+      <c r="G115" s="15" t="inlineStr">
         <is>
           <t>1. Thêm cùng một thiết bị 2 lần vào bảng
 2. Ở cả 2 dòng chọn cùng một serial
@@ -7293,153 +7432,15 @@
 4. Bấm Lưu và gửi rồi Xác nhận</t>
         </is>
       </c>
-      <c r="H113" s="15" t="inlineStr">
+      <c r="H115" s="15" t="inlineStr">
         <is>
           <t>Serial: 30021180069 (cả 2 dòng)</t>
         </is>
       </c>
-      <c r="I113" s="15" t="inlineStr">
+      <c r="I115" s="15" t="inlineStr">
         <is>
           <t>- Hệ thống chặn, báo bị trùng serial thiết bị
 - Báo lỗi ở CẢ HAI dòng bị trùng</t>
-        </is>
-      </c>
-      <c r="J113" s="15" t="inlineStr"/>
-      <c r="K113" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="L113" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="M113" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="N113" s="15" t="inlineStr"/>
-      <c r="O113" s="16" t="inlineStr"/>
-      <c r="P113" s="16" t="inlineStr"/>
-      <c r="Q113" s="16" t="inlineStr"/>
-    </row>
-    <row r="114" ht="34" customHeight="1">
-      <c r="A114" s="15" t="inlineStr">
-        <is>
-          <t>YC sửa chữa - bảo hành</t>
-        </is>
-      </c>
-      <c r="B114" s="15" t="inlineStr">
-        <is>
-          <t>RÀNG BUỘC NHẬP LIỆU</t>
-        </is>
-      </c>
-      <c r="C114" s="16" t="inlineStr">
-        <is>
-          <t>TC_08.004</t>
-        </is>
-      </c>
-      <c r="D114" s="15" t="inlineStr">
-        <is>
-          <t>Bắt buộc nhập serial khi thiết bị chưa có serial trong hệ thống</t>
-        </is>
-      </c>
-      <c r="E114" s="16" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="F114" s="15" t="inlineStr">
-        <is>
-          <t>Chọn thiết bị chưa được khai serial nào.</t>
-        </is>
-      </c>
-      <c r="G114" s="15" t="inlineStr">
-        <is>
-          <t>1. Thêm thiết bị đó vào bảng
-2. Nhập mô tả yêu cầu, để trống ô serial
-3. Bấm Lưu và gửi rồi Xác nhận</t>
-        </is>
-      </c>
-      <c r="H114" s="15" t="inlineStr">
-        <is>
-          <t>Serial: (để trống)</t>
-        </is>
-      </c>
-      <c r="I114" s="15" t="inlineStr">
-        <is>
-          <t>- Hệ thống chặn, báo bắt buộc phải nhập tại ô serial của dòng đó</t>
-        </is>
-      </c>
-      <c r="J114" s="15" t="inlineStr"/>
-      <c r="K114" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="L114" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="M114" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="N114" s="15" t="inlineStr"/>
-      <c r="O114" s="16" t="inlineStr"/>
-      <c r="P114" s="16" t="inlineStr"/>
-      <c r="Q114" s="16" t="inlineStr"/>
-    </row>
-    <row r="115" ht="35" customHeight="1">
-      <c r="A115" s="15" t="inlineStr">
-        <is>
-          <t>YC sửa chữa - bảo hành</t>
-        </is>
-      </c>
-      <c r="B115" s="15" t="inlineStr">
-        <is>
-          <t>RÀNG BUỘC NHẬP LIỆU</t>
-        </is>
-      </c>
-      <c r="C115" s="16" t="inlineStr">
-        <is>
-          <t>TC_08.005</t>
-        </is>
-      </c>
-      <c r="D115" s="15" t="inlineStr">
-        <is>
-          <t>Khách hàng là cá nhân thì không có danh sách người liên hệ</t>
-        </is>
-      </c>
-      <c r="E115" s="16" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F115" s="15" t="inlineStr">
-        <is>
-          <t>Có khách hàng thuộc loại cá nhân.</t>
-        </is>
-      </c>
-      <c r="G115" s="15" t="inlineStr">
-        <is>
-          <t>1. Tạo phiếu, chọn khách hàng cá nhân đó
-2. Xem ô Người liên hệ</t>
-        </is>
-      </c>
-      <c r="H115" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I115" s="15" t="inlineStr">
-        <is>
-          <t>- Ô Người liên hệ chuyển thành ô chỉ đọc, điền sẵn thông tin của chính khách
-- Không mở được danh sách chọn</t>
         </is>
       </c>
       <c r="J115" s="15" t="inlineStr"/>
@@ -7476,39 +7477,39 @@
       </c>
       <c r="C116" s="16" t="inlineStr">
         <is>
-          <t>TC_08.006</t>
+          <t>TC_08.004</t>
         </is>
       </c>
       <c r="D116" s="15" t="inlineStr">
         <is>
-          <t>Lưu nháp không cần chọn thiết bị</t>
+          <t>Bắt buộc nhập serial khi thiết bị chưa có serial trong hệ thống</t>
         </is>
       </c>
       <c r="E116" s="16" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="F116" s="15" t="inlineStr">
         <is>
-          <t>Màn Tạo mới, chỉ chọn khách hàng.</t>
+          <t>Chọn thiết bị chưa được khai serial nào.</t>
         </is>
       </c>
       <c r="G116" s="15" t="inlineStr">
         <is>
-          <t>1. Chọn khách hàng
-2. Bấm Lưu nháp ngay</t>
+          <t>1. Thêm thiết bị đó vào bảng
+2. Nhập mô tả yêu cầu, để trống ô serial
+3. Bấm Lưu và gửi rồi Xác nhận</t>
         </is>
       </c>
       <c r="H116" s="15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Serial: (để trống)</t>
         </is>
       </c>
       <c r="I116" s="15" t="inlineStr">
         <is>
-          <t>- Lưu thành công, phiếu ở “Đang tạo”
-- ⚠️ Ràng buộc thiết bị chỉ áp dụng khi gửi đi</t>
+          <t>- Hệ thống chặn, báo bắt buộc phải nhập tại ô serial của dòng đó</t>
         </is>
       </c>
       <c r="J116" s="15" t="inlineStr"/>
@@ -7532,7 +7533,7 @@
       <c r="P116" s="16" t="inlineStr"/>
       <c r="Q116" s="16" t="inlineStr"/>
     </row>
-    <row r="117" ht="34" customHeight="1">
+    <row r="117" ht="35" customHeight="1">
       <c r="A117" s="15" t="inlineStr">
         <is>
           <t>YC sửa chữa - bảo hành</t>
@@ -7545,27 +7546,28 @@
       </c>
       <c r="C117" s="16" t="inlineStr">
         <is>
-          <t>TC_08.007</t>
+          <t>TC_08.005</t>
         </is>
       </c>
       <c r="D117" s="15" t="inlineStr">
         <is>
-          <t>Bắt buộc chọn khách hàng</t>
+          <t>Khách hàng là cá nhân thì không có danh sách người liên hệ</t>
         </is>
       </c>
       <c r="E117" s="16" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F117" s="15" t="inlineStr">
         <is>
-          <t>Màn Tạo mới, chưa chọn gì.</t>
+          <t>Có khách hàng thuộc loại cá nhân.</t>
         </is>
       </c>
       <c r="G117" s="15" t="inlineStr">
         <is>
-          <t>1. Bấm Lưu nháp</t>
+          <t>1. Tạo phiếu, chọn khách hàng cá nhân đó
+2. Xem ô Người liên hệ</t>
         </is>
       </c>
       <c r="H117" s="15" t="inlineStr">
@@ -7575,8 +7577,8 @@
       </c>
       <c r="I117" s="15" t="inlineStr">
         <is>
-          <t>- Hệ thống chặn, báo lỗi đỏ ngay dưới ô Khách hàng
-- Không tạo ra phiếu nào</t>
+          <t>- Ô Người liên hệ chuyển thành ô chỉ đọc, điền sẵn thông tin của chính khách
+- Không mở được danh sách chọn</t>
         </is>
       </c>
       <c r="J117" s="15" t="inlineStr"/>
@@ -7600,30 +7602,76 @@
       <c r="P117" s="16" t="inlineStr"/>
       <c r="Q117" s="16" t="inlineStr"/>
     </row>
-    <row r="118" ht="26" customHeight="1">
-      <c r="A118" s="13" t="n"/>
-      <c r="B118" s="13" t="n"/>
-      <c r="C118" s="14" t="inlineStr">
-        <is>
-          <t>IX. CÔ LẬP DỮ LIỆU &amp; THAO TÁC ĐỒNG THỜI</t>
-        </is>
-      </c>
-      <c r="D118" s="4" t="n"/>
-      <c r="E118" s="4" t="n"/>
-      <c r="F118" s="4" t="n"/>
-      <c r="G118" s="4" t="n"/>
-      <c r="H118" s="4" t="n"/>
-      <c r="I118" s="4" t="n"/>
-      <c r="J118" s="4" t="n"/>
-      <c r="K118" s="4" t="n"/>
-      <c r="L118" s="4" t="n"/>
-      <c r="M118" s="4" t="n"/>
-      <c r="N118" s="4" t="n"/>
-      <c r="O118" s="4" t="n"/>
-      <c r="P118" s="4" t="n"/>
-      <c r="Q118" s="5" t="n"/>
-    </row>
-    <row r="119" ht="42" customHeight="1">
+    <row r="118" ht="34" customHeight="1">
+      <c r="A118" s="15" t="inlineStr">
+        <is>
+          <t>YC sửa chữa - bảo hành</t>
+        </is>
+      </c>
+      <c r="B118" s="15" t="inlineStr">
+        <is>
+          <t>RÀNG BUỘC NHẬP LIỆU</t>
+        </is>
+      </c>
+      <c r="C118" s="16" t="inlineStr">
+        <is>
+          <t>TC_08.006</t>
+        </is>
+      </c>
+      <c r="D118" s="15" t="inlineStr">
+        <is>
+          <t>Lưu nháp không cần chọn thiết bị</t>
+        </is>
+      </c>
+      <c r="E118" s="16" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F118" s="15" t="inlineStr">
+        <is>
+          <t>Màn Tạo mới, chỉ chọn khách hàng.</t>
+        </is>
+      </c>
+      <c r="G118" s="15" t="inlineStr">
+        <is>
+          <t>1. Chọn khách hàng
+2. Bấm Lưu nháp ngay</t>
+        </is>
+      </c>
+      <c r="H118" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I118" s="15" t="inlineStr">
+        <is>
+          <t>- Lưu thành công, phiếu ở “Đang tạo”
+- ⚠️ Ràng buộc thiết bị chỉ áp dụng khi gửi đi</t>
+        </is>
+      </c>
+      <c r="J118" s="15" t="inlineStr"/>
+      <c r="K118" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="L118" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="M118" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="N118" s="15" t="inlineStr"/>
+      <c r="O118" s="16" t="inlineStr"/>
+      <c r="P118" s="16" t="inlineStr"/>
+      <c r="Q118" s="16" t="inlineStr"/>
+    </row>
+    <row r="119" ht="34" customHeight="1">
       <c r="A119" s="15" t="inlineStr">
         <is>
           <t>YC sửa chữa - bảo hành</t>
@@ -7631,44 +7679,43 @@
       </c>
       <c r="B119" s="15" t="inlineStr">
         <is>
-          <t>CÔ LẬP DỮ LIỆU &amp; THAO TÁC ĐỒNG THỜI</t>
+          <t>RÀNG BUỘC NHẬP LIỆU</t>
         </is>
       </c>
       <c r="C119" s="16" t="inlineStr">
         <is>
-          <t>TC_09.001</t>
+          <t>TC_08.007</t>
         </is>
       </c>
       <c r="D119" s="15" t="inlineStr">
         <is>
-          <t>Hai người cùng thao tác trên một phiếu</t>
+          <t>Bắt buộc chọn khách hàng</t>
         </is>
       </c>
       <c r="E119" s="16" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="F119" s="15" t="inlineStr">
         <is>
-          <t>Phiếu đang “Chờ xử lý”, cả E và F cùng thuộc phòng tiếp nhận và cùng mở phiếu.</t>
+          <t>Màn Tạo mới, chưa chọn gì.</t>
         </is>
       </c>
       <c r="G119" s="15" t="inlineStr">
         <is>
-          <t>1. E bấm Từ chối và nhập lý do, xác nhận
-2. F (chưa tải lại trang) bấm Chuyển phòng tiếp nhận và xác nhận</t>
+          <t>1. Bấm Lưu nháp</t>
         </is>
       </c>
       <c r="H119" s="15" t="inlineStr">
         <is>
-          <t>Lý do từ chối: “trùng phiếu”</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I119" s="15" t="inlineStr">
         <is>
-          <t>- Thao tác của F không được thực hiện hoặc hệ thống báo dữ liệu đã thay đổi
-- Không treo trang, tải lại thấy phiếu ở “Đang tạo”</t>
+          <t>- Hệ thống chặn, báo lỗi đỏ ngay dưới ô Khách hàng
+- Không tạo ra phiếu nào</t>
         </is>
       </c>
       <c r="J119" s="15" t="inlineStr"/>
@@ -7692,121 +7739,75 @@
       <c r="P119" s="16" t="inlineStr"/>
       <c r="Q119" s="16" t="inlineStr"/>
     </row>
-    <row r="120" ht="34" customHeight="1">
-      <c r="A120" s="15" t="inlineStr">
-        <is>
-          <t>YC sửa chữa - bảo hành</t>
-        </is>
-      </c>
-      <c r="B120" s="15" t="inlineStr">
+    <row r="120" ht="26" customHeight="1">
+      <c r="A120" s="13" t="n"/>
+      <c r="B120" s="13" t="n"/>
+      <c r="C120" s="14" t="inlineStr">
+        <is>
+          <t>IX. CÔ LẬP DỮ LIỆU &amp; THAO TÁC ĐỒNG THỜI</t>
+        </is>
+      </c>
+      <c r="D120" s="4" t="n"/>
+      <c r="E120" s="4" t="n"/>
+      <c r="F120" s="4" t="n"/>
+      <c r="G120" s="4" t="n"/>
+      <c r="H120" s="4" t="n"/>
+      <c r="I120" s="4" t="n"/>
+      <c r="J120" s="4" t="n"/>
+      <c r="K120" s="4" t="n"/>
+      <c r="L120" s="4" t="n"/>
+      <c r="M120" s="4" t="n"/>
+      <c r="N120" s="4" t="n"/>
+      <c r="O120" s="4" t="n"/>
+      <c r="P120" s="4" t="n"/>
+      <c r="Q120" s="5" t="n"/>
+    </row>
+    <row r="121" ht="42" customHeight="1">
+      <c r="A121" s="15" t="inlineStr">
+        <is>
+          <t>YC sửa chữa - bảo hành</t>
+        </is>
+      </c>
+      <c r="B121" s="15" t="inlineStr">
         <is>
           <t>CÔ LẬP DỮ LIỆU &amp; THAO TÁC ĐỒNG THỜI</t>
         </is>
       </c>
-      <c r="C120" s="16" t="inlineStr">
-        <is>
-          <t>TC_09.002</t>
-        </is>
-      </c>
-      <c r="D120" s="15" t="inlineStr">
-        <is>
-          <t>Xóa phiếu vừa bị người khác xóa</t>
-        </is>
-      </c>
-      <c r="E120" s="16" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="F120" s="15" t="inlineStr">
-        <is>
-          <t>Hai cửa sổ trình duyệt cùng mở danh sách, cùng thấy phiếu nháp X.</t>
-        </is>
-      </c>
-      <c r="G120" s="15" t="inlineStr">
-        <is>
-          <t>1. Cửa sổ 1 xóa phiếu X
-2. Cửa sổ 2 (chưa tải lại) cũng bấm Xóa phiếu X và xác nhận</t>
-        </is>
-      </c>
-      <c r="H120" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I120" s="15" t="inlineStr">
-        <is>
-          <t>- Cửa sổ 2 báo dữ liệu đã thay đổi, không treo trang
-- Danh sách tải lại không còn phiếu X</t>
-        </is>
-      </c>
-      <c r="J120" s="15" t="inlineStr"/>
-      <c r="K120" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="L120" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="M120" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="N120" s="15" t="inlineStr"/>
-      <c r="O120" s="16" t="inlineStr"/>
-      <c r="P120" s="16" t="inlineStr"/>
-      <c r="Q120" s="16" t="inlineStr"/>
-    </row>
-    <row r="121" ht="39" customHeight="1">
-      <c r="A121" s="15" t="inlineStr">
-        <is>
-          <t>YC sửa chữa - bảo hành</t>
-        </is>
-      </c>
-      <c r="B121" s="15" t="inlineStr">
-        <is>
-          <t>CÔ LẬP DỮ LIỆU &amp; THAO TÁC ĐỒNG THỜI</t>
-        </is>
-      </c>
       <c r="C121" s="16" t="inlineStr">
         <is>
-          <t>TC_09.003</t>
+          <t>TC_09.001</t>
         </is>
       </c>
       <c r="D121" s="15" t="inlineStr">
         <is>
-          <t>Dữ liệu lập bên ERP hiện ngay bên đây</t>
+          <t>Hai người cùng thao tác trên một phiếu</t>
         </is>
       </c>
       <c r="E121" s="16" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F121" s="15" t="inlineStr">
         <is>
-          <t>Có tài khoản dùng được cả 2 cổng.</t>
+          <t>Phiếu đang “Chờ xử lý”, cả E và F cùng thuộc phòng tiếp nhận và cùng mở phiếu.</t>
         </is>
       </c>
       <c r="G121" s="15" t="inlineStr">
         <is>
-          <t>1. Lập 1 phiếu bên phần mềm ERP và gửi đi
-2. Sang màn hình này, tìm theo số phiếu vừa lập</t>
+          <t>1. E bấm Từ chối và nhập lý do, xác nhận
+2. F (chưa tải lại trang) bấm Chuyển phòng tiếp nhận và xác nhận</t>
         </is>
       </c>
       <c r="H121" s="15" t="inlineStr">
         <is>
-          <t>Số phiếu vừa lập bên ERP</t>
+          <t>Lý do từ chối: “trùng phiếu”</t>
         </is>
       </c>
       <c r="I121" s="15" t="inlineStr">
         <is>
-          <t>- Tìm thấy đúng phiếu đó, trạng thái “Chờ xử lý”
-- Mở chi tiết thấy đủ khách hàng và các dòng thiết bị đã nhập bên ERP</t>
+          <t>- Thao tác của F không được thực hiện hoặc hệ thống báo dữ liệu đã thay đổi
+- Không treo trang, tải lại thấy phiếu ở “Đang tạo”</t>
         </is>
       </c>
       <c r="J121" s="15" t="inlineStr"/>
@@ -7830,61 +7831,199 @@
       <c r="P121" s="16" t="inlineStr"/>
       <c r="Q121" s="16" t="inlineStr"/>
     </row>
-    <row r="122" ht="26" customHeight="1">
-      <c r="A122" s="13" t="n"/>
-      <c r="B122" s="13" t="n"/>
-      <c r="C122" s="14" t="inlineStr">
+    <row r="122" ht="34" customHeight="1">
+      <c r="A122" s="15" t="inlineStr">
+        <is>
+          <t>YC sửa chữa - bảo hành</t>
+        </is>
+      </c>
+      <c r="B122" s="15" t="inlineStr">
+        <is>
+          <t>CÔ LẬP DỮ LIỆU &amp; THAO TÁC ĐỒNG THỜI</t>
+        </is>
+      </c>
+      <c r="C122" s="16" t="inlineStr">
+        <is>
+          <t>TC_09.002</t>
+        </is>
+      </c>
+      <c r="D122" s="15" t="inlineStr">
+        <is>
+          <t>Xóa phiếu vừa bị người khác xóa</t>
+        </is>
+      </c>
+      <c r="E122" s="16" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F122" s="15" t="inlineStr">
+        <is>
+          <t>Hai cửa sổ trình duyệt cùng mở danh sách, cùng thấy phiếu nháp X.</t>
+        </is>
+      </c>
+      <c r="G122" s="15" t="inlineStr">
+        <is>
+          <t>1. Cửa sổ 1 xóa phiếu X
+2. Cửa sổ 2 (chưa tải lại) cũng bấm Xóa phiếu X và xác nhận</t>
+        </is>
+      </c>
+      <c r="H122" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I122" s="15" t="inlineStr">
+        <is>
+          <t>- Cửa sổ 2 báo dữ liệu đã thay đổi, không treo trang
+- Danh sách tải lại không còn phiếu X</t>
+        </is>
+      </c>
+      <c r="J122" s="15" t="inlineStr"/>
+      <c r="K122" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="L122" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="M122" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="N122" s="15" t="inlineStr"/>
+      <c r="O122" s="16" t="inlineStr"/>
+      <c r="P122" s="16" t="inlineStr"/>
+      <c r="Q122" s="16" t="inlineStr"/>
+    </row>
+    <row r="123" ht="39" customHeight="1">
+      <c r="A123" s="15" t="inlineStr">
+        <is>
+          <t>YC sửa chữa - bảo hành</t>
+        </is>
+      </c>
+      <c r="B123" s="15" t="inlineStr">
+        <is>
+          <t>CÔ LẬP DỮ LIỆU &amp; THAO TÁC ĐỒNG THỜI</t>
+        </is>
+      </c>
+      <c r="C123" s="16" t="inlineStr">
+        <is>
+          <t>TC_09.003</t>
+        </is>
+      </c>
+      <c r="D123" s="15" t="inlineStr">
+        <is>
+          <t>Dữ liệu lập bên ERP hiện ngay bên đây</t>
+        </is>
+      </c>
+      <c r="E123" s="16" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F123" s="15" t="inlineStr">
+        <is>
+          <t>Có tài khoản dùng được cả 2 cổng.</t>
+        </is>
+      </c>
+      <c r="G123" s="15" t="inlineStr">
+        <is>
+          <t>1. Lập 1 phiếu bên phần mềm ERP và gửi đi
+2. Sang màn hình này, tìm theo số phiếu vừa lập</t>
+        </is>
+      </c>
+      <c r="H123" s="15" t="inlineStr">
+        <is>
+          <t>Số phiếu vừa lập bên ERP</t>
+        </is>
+      </c>
+      <c r="I123" s="15" t="inlineStr">
+        <is>
+          <t>- Tìm thấy đúng phiếu đó, trạng thái “Chờ xử lý”
+- Mở chi tiết thấy đủ khách hàng và các dòng thiết bị đã nhập bên ERP</t>
+        </is>
+      </c>
+      <c r="J123" s="15" t="inlineStr"/>
+      <c r="K123" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="L123" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="M123" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="N123" s="15" t="inlineStr"/>
+      <c r="O123" s="16" t="inlineStr"/>
+      <c r="P123" s="16" t="inlineStr"/>
+      <c r="Q123" s="16" t="inlineStr"/>
+    </row>
+    <row r="124" ht="26" customHeight="1">
+      <c r="A124" s="13" t="n"/>
+      <c r="B124" s="13" t="n"/>
+      <c r="C124" s="14" t="inlineStr">
         <is>
           <t>X. LUỒNG NGHIỆP VỤ ĐẦU – CUỐI</t>
         </is>
       </c>
-      <c r="D122" s="4" t="n"/>
-      <c r="E122" s="4" t="n"/>
-      <c r="F122" s="4" t="n"/>
-      <c r="G122" s="4" t="n"/>
-      <c r="H122" s="4" t="n"/>
-      <c r="I122" s="4" t="n"/>
-      <c r="J122" s="4" t="n"/>
-      <c r="K122" s="4" t="n"/>
-      <c r="L122" s="4" t="n"/>
-      <c r="M122" s="4" t="n"/>
-      <c r="N122" s="4" t="n"/>
-      <c r="O122" s="4" t="n"/>
-      <c r="P122" s="4" t="n"/>
-      <c r="Q122" s="5" t="n"/>
-    </row>
-    <row r="123" ht="112" customHeight="1">
-      <c r="A123" s="15" t="inlineStr">
-        <is>
-          <t>YC sửa chữa - bảo hành</t>
-        </is>
-      </c>
-      <c r="B123" s="15" t="inlineStr">
+      <c r="D124" s="4" t="n"/>
+      <c r="E124" s="4" t="n"/>
+      <c r="F124" s="4" t="n"/>
+      <c r="G124" s="4" t="n"/>
+      <c r="H124" s="4" t="n"/>
+      <c r="I124" s="4" t="n"/>
+      <c r="J124" s="4" t="n"/>
+      <c r="K124" s="4" t="n"/>
+      <c r="L124" s="4" t="n"/>
+      <c r="M124" s="4" t="n"/>
+      <c r="N124" s="4" t="n"/>
+      <c r="O124" s="4" t="n"/>
+      <c r="P124" s="4" t="n"/>
+      <c r="Q124" s="5" t="n"/>
+    </row>
+    <row r="125" ht="112" customHeight="1">
+      <c r="A125" s="15" t="inlineStr">
+        <is>
+          <t>YC sửa chữa - bảo hành</t>
+        </is>
+      </c>
+      <c r="B125" s="15" t="inlineStr">
         <is>
           <t>LUỒNG NGHIỆP VỤ ĐẦU – CUỐI</t>
         </is>
       </c>
-      <c r="C123" s="16" t="inlineStr">
+      <c r="C125" s="16" t="inlineStr">
         <is>
           <t>TC_10.001</t>
         </is>
       </c>
-      <c r="D123" s="15" t="inlineStr">
+      <c r="D125" s="15" t="inlineStr">
         <is>
           <t>Luồng đầy đủ: lập → gửi → từ chối → sửa → gửi lại → chuyển phòng</t>
         </is>
       </c>
-      <c r="E123" s="16" t="inlineStr">
+      <c r="E125" s="16" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="F123" s="15" t="inlineStr">
+      <c r="F125" s="15" t="inlineStr">
         <is>
           <t>Nhân viên G (người lập), phòng tiếp nhận Kỹ thuật có nhân viên E, phòng Bảo hành có nhân viên H. Khách hàng có sẵn thiết bị.</t>
         </is>
       </c>
-      <c r="G123" s="15" t="inlineStr">
+      <c r="G125" s="15" t="inlineStr">
         <is>
           <t>1. G lập phiếu, chọn khách, thêm 1 thiết bị, Lưu nháp
 2. G mở lại, điền đủ thông tin, Lưu và gửi (phòng tiếp nhận: Kỹ thuật)
@@ -7894,12 +8033,12 @@
 6. H mở chuông thông báo</t>
         </is>
       </c>
-      <c r="H123" s="15" t="inlineStr">
+      <c r="H125" s="15" t="inlineStr">
         <is>
           <t>Lý do từ chối: “Thiếu ảnh hiện trạng thiết bị”</t>
         </is>
       </c>
-      <c r="I123" s="15" t="inlineStr">
+      <c r="I125" s="15" t="inlineStr">
         <is>
           <t>- Bước 1: phiếu “Đang tạo”, đã có số phiếu
 - Bước 2: phiếu “Chờ xử lý”, E có thông báo Chờ duyệt
@@ -7909,59 +8048,59 @@
 - Xuyên suốt: mỗi trạng thái chỉ hiện đúng các nút được phép</t>
         </is>
       </c>
-      <c r="J123" s="15" t="inlineStr"/>
-      <c r="K123" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="L123" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="M123" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="N123" s="15" t="inlineStr"/>
-      <c r="O123" s="16" t="inlineStr"/>
-      <c r="P123" s="16" t="inlineStr"/>
-      <c r="Q123" s="16" t="inlineStr"/>
-    </row>
-    <row r="124" ht="43" customHeight="1">
-      <c r="A124" s="15" t="inlineStr">
-        <is>
-          <t>YC sửa chữa - bảo hành</t>
-        </is>
-      </c>
-      <c r="B124" s="15" t="inlineStr">
+      <c r="J125" s="15" t="inlineStr"/>
+      <c r="K125" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="L125" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="M125" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="N125" s="15" t="inlineStr"/>
+      <c r="O125" s="16" t="inlineStr"/>
+      <c r="P125" s="16" t="inlineStr"/>
+      <c r="Q125" s="16" t="inlineStr"/>
+    </row>
+    <row r="126" ht="43" customHeight="1">
+      <c r="A126" s="15" t="inlineStr">
+        <is>
+          <t>YC sửa chữa - bảo hành</t>
+        </is>
+      </c>
+      <c r="B126" s="15" t="inlineStr">
         <is>
           <t>LUỒNG NGHIỆP VỤ ĐẦU – CUỐI</t>
         </is>
       </c>
-      <c r="C124" s="16" t="inlineStr">
+      <c r="C126" s="16" t="inlineStr">
         <is>
           <t>TC_10.002</t>
         </is>
       </c>
-      <c r="D124" s="15" t="inlineStr">
+      <c r="D126" s="15" t="inlineStr">
         <is>
           <t>Luồng lập nhanh rồi xóa</t>
         </is>
       </c>
-      <c r="E124" s="16" t="inlineStr">
+      <c r="E126" s="16" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F124" s="15" t="inlineStr">
+      <c r="F126" s="15" t="inlineStr">
         <is>
           <t>Nhân viên G có quyền lập phiếu.</t>
         </is>
       </c>
-      <c r="G124" s="15" t="inlineStr">
+      <c r="G126" s="15" t="inlineStr">
         <is>
           <t>1. G lập phiếu, Lưu nháp
 2. G mở lại, thêm thiết bị, Lưu nháp
@@ -7969,82 +8108,82 @@
 4. Kiểm tra lại danh sách và tìm theo số phiếu vừa xóa</t>
         </is>
       </c>
-      <c r="H124" s="15" t="inlineStr">
+      <c r="H126" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I124" s="15" t="inlineStr">
+      <c r="I126" s="15" t="inlineStr">
         <is>
           <t>- Xóa xong không tìm thấy phiếu bằng số phiếu
 - Tổng N trở về như trước khi lập</t>
         </is>
       </c>
-      <c r="J124" s="15" t="inlineStr"/>
-      <c r="K124" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="L124" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="M124" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="N124" s="15" t="inlineStr"/>
-      <c r="O124" s="16" t="inlineStr"/>
-      <c r="P124" s="16" t="inlineStr"/>
-      <c r="Q124" s="16" t="inlineStr"/>
-    </row>
-    <row r="125" ht="170" customHeight="1">
-      <c r="A125" s="15" t="inlineStr">
-        <is>
-          <t>YC sửa chữa - bảo hành</t>
-        </is>
-      </c>
-      <c r="B125" s="15" t="inlineStr">
+      <c r="J126" s="15" t="inlineStr"/>
+      <c r="K126" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="L126" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="M126" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="N126" s="15" t="inlineStr"/>
+      <c r="O126" s="16" t="inlineStr"/>
+      <c r="P126" s="16" t="inlineStr"/>
+      <c r="Q126" s="16" t="inlineStr"/>
+    </row>
+    <row r="127" ht="170" customHeight="1">
+      <c r="A127" s="15" t="inlineStr">
+        <is>
+          <t>YC sửa chữa - bảo hành</t>
+        </is>
+      </c>
+      <c r="B127" s="15" t="inlineStr">
         <is>
           <t>LUỒNG NGHIỆP VỤ ĐẦU – CUỐI</t>
         </is>
       </c>
-      <c r="C125" s="16" t="inlineStr">
+      <c r="C127" s="16" t="inlineStr">
         <is>
           <t>TC_10.003</t>
         </is>
       </c>
-      <c r="D125" s="15" t="inlineStr">
+      <c r="D127" s="15" t="inlineStr">
         <is>
           <t>Phiếu đi tiếp sang Phiếu xử lý yêu cầu</t>
         </is>
       </c>
-      <c r="E125" s="16" t="inlineStr">
+      <c r="E127" s="16" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="F125" s="15" t="inlineStr">
+      <c r="F127" s="15" t="inlineStr">
         <is>
           <t>Phiếu đang “Chờ xử lý”, người đăng nhập có quyền “Xử lý yêu cầu sửa chữa”.</t>
         </is>
       </c>
-      <c r="G125" s="15" t="inlineStr">
+      <c r="G127" s="15" t="inlineStr">
         <is>
           <t>1. Bấm nút Tạo phiếu xử lý yêu cầu
 2. Hoàn tất phiếu xử lý bên màn tương ứng
 3. Quay lại màn danh sách yêu cầu, tìm phiếu ban đầu</t>
         </is>
       </c>
-      <c r="H125" s="15" t="inlineStr">
+      <c r="H127" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I125" s="15" t="inlineStr">
+      <c r="I127" s="15" t="inlineStr">
         <is>
           <t>- Trạng thái phiếu chuyển sang “Đã xử lý” (nếu phiếu xử lý được gửi đi chờ cung cấp thông tin) hoặc “Đã tư vấn điện thoại” (nếu mọi thiết bị đều chọn phương án tư vấn qua điện thoại)
 - Cột Người xử lý và Ngày xử lý của phiếu được điền
@@ -8053,26 +8192,26 @@
 - ⚠️ Màn Phiếu xử lý yêu cầu phải đã có trên hệ thống mới chạy được bước này</t>
         </is>
       </c>
-      <c r="J125" s="15" t="inlineStr"/>
-      <c r="K125" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="L125" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="M125" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="N125" s="15" t="inlineStr"/>
-      <c r="O125" s="16" t="inlineStr"/>
-      <c r="P125" s="16" t="inlineStr"/>
-      <c r="Q125" s="16" t="inlineStr"/>
+      <c r="J127" s="15" t="inlineStr"/>
+      <c r="K127" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="L127" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="M127" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="N127" s="15" t="inlineStr"/>
+      <c r="O127" s="16" t="inlineStr"/>
+      <c r="P127" s="16" t="inlineStr"/>
+      <c r="Q127" s="16" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="43">
@@ -8081,11 +8220,12 @@
     <mergeCell ref="C54:Q54"/>
     <mergeCell ref="I15:J15"/>
     <mergeCell ref="C99:Q99"/>
+    <mergeCell ref="C112:Q112"/>
     <mergeCell ref="K15:L15"/>
     <mergeCell ref="A11:E11"/>
     <mergeCell ref="I11:J11"/>
+    <mergeCell ref="C124:Q124"/>
     <mergeCell ref="C80:Q80"/>
-    <mergeCell ref="C118:Q118"/>
     <mergeCell ref="B6:N6"/>
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="C59:Q59"/>
@@ -8096,12 +8236,11 @@
     <mergeCell ref="B4:N4"/>
     <mergeCell ref="C36:Q36"/>
     <mergeCell ref="O12:Q12"/>
-    <mergeCell ref="C110:Q110"/>
+    <mergeCell ref="C120:Q120"/>
     <mergeCell ref="B7:N7"/>
     <mergeCell ref="B3:N3"/>
     <mergeCell ref="O11:Q11"/>
     <mergeCell ref="M13:N13"/>
-    <mergeCell ref="C122:Q122"/>
     <mergeCell ref="I12:J12"/>
     <mergeCell ref="O14:Q14"/>
     <mergeCell ref="M15:N15"/>
@@ -8121,10 +8260,10 @@
     <mergeCell ref="B10:N10"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="K18:M175" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K18:M177" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Passed,Failed,Pending,Not Executed"</formula1>
     </dataValidation>
-    <dataValidation sqref="O18:Q175" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O18:Q177" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"P,F,PE"</formula1>
     </dataValidation>
   </dataValidations>
